--- a/notebooks/XGBoost/opj_predictions_comparison_2019.xlsx
+++ b/notebooks/XGBoost/opj_predictions_comparison_2019.xlsx
@@ -485,7 +485,7 @@
         <v>2019</v>
       </c>
       <c r="C2" t="n">
-        <v>70.84207153320312</v>
+        <v>70.85223388671875</v>
       </c>
       <c r="D2" t="n">
         <v>70.92</v>
@@ -494,13 +494,13 @@
         <v>70.53</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07792846679687671</v>
+        <v>0.06776611328125171</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07792846679687671</v>
+        <v>0.06776611328125171</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1098822148856129</v>
+        <v>0.09555289520763072</v>
       </c>
       <c r="I2" t="n">
         <v>18</v>
@@ -516,7 +516,7 @@
         <v>2019</v>
       </c>
       <c r="C3" t="n">
-        <v>69.21950531005859</v>
+        <v>69.20698547363281</v>
       </c>
       <c r="D3" t="n">
         <v>68.42</v>
@@ -525,16 +525,16 @@
         <v>68.90000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.799505310058592</v>
+        <v>-0.7869854736328108</v>
       </c>
       <c r="G3" t="n">
-        <v>0.799505310058592</v>
+        <v>0.7869854736328108</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.168525738173914</v>
+        <v>-1.150227234190019</v>
       </c>
       <c r="I3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         <v>2019</v>
       </c>
       <c r="C4" t="n">
-        <v>71.85634613037109</v>
+        <v>71.78624725341797</v>
       </c>
       <c r="D4" t="n">
         <v>71.56</v>
@@ -556,16 +556,16 @@
         <v>71.44</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2963461303710915</v>
+        <v>-0.2262472534179665</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2963461303710915</v>
+        <v>0.2262472534179665</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4141225969411563</v>
+        <v>-0.3161644122665825</v>
       </c>
       <c r="I4" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -578,7 +578,7 @@
         <v>2019</v>
       </c>
       <c r="C5" t="n">
-        <v>73.24061584472656</v>
+        <v>73.26103210449219</v>
       </c>
       <c r="D5" t="n">
         <v>72.95</v>
@@ -587,16 +587,16 @@
         <v>72.73</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2906158447265597</v>
+        <v>-0.3110321044921847</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2906158447265597</v>
+        <v>0.3110321044921847</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3983767576786287</v>
+        <v>-0.4263634057466548</v>
       </c>
       <c r="I5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +609,7 @@
         <v>2019</v>
       </c>
       <c r="C6" t="n">
-        <v>73.96302795410156</v>
+        <v>74.02190399169922</v>
       </c>
       <c r="D6" t="n">
         <v>74.26000000000001</v>
@@ -618,16 +618,16 @@
         <v>73.70999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2969720458984426</v>
+        <v>0.2380960083007864</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2969720458984426</v>
+        <v>0.2380960083007864</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3999084916488589</v>
+        <v>0.3206248428505068</v>
       </c>
       <c r="I6" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -640,7 +640,7 @@
         <v>2019</v>
       </c>
       <c r="C7" t="n">
-        <v>71.97099304199219</v>
+        <v>72.02182006835938</v>
       </c>
       <c r="D7" t="n">
         <v>72.14</v>
@@ -649,16 +649,16 @@
         <v>71.56999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1690069580078131</v>
+        <v>0.1181799316406256</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1690069580078131</v>
+        <v>0.1181799316406256</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2342763487771182</v>
+        <v>0.1638202545614438</v>
       </c>
       <c r="I7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -671,7 +671,7 @@
         <v>2019</v>
       </c>
       <c r="C8" t="n">
-        <v>71.70659637451172</v>
+        <v>71.69386291503906</v>
       </c>
       <c r="D8" t="n">
         <v>72</v>
@@ -680,16 +680,16 @@
         <v>71.34999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2934036254882812</v>
+        <v>0.3061370849609375</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2934036254882812</v>
+        <v>0.3061370849609375</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4075050354003906</v>
+        <v>0.4251903957790799</v>
       </c>
       <c r="I8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -702,7 +702,7 @@
         <v>2019</v>
       </c>
       <c r="C9" t="n">
-        <v>73.87258911132812</v>
+        <v>73.84315490722656</v>
       </c>
       <c r="D9" t="n">
         <v>74.11</v>
@@ -711,16 +711,16 @@
         <v>73.5</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2374108886718744</v>
+        <v>0.2668450927734369</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2374108886718744</v>
+        <v>0.2668450927734369</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3203493302818438</v>
+        <v>0.3600662431162285</v>
       </c>
       <c r="I9" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         <v>2019</v>
       </c>
       <c r="C10" t="n">
-        <v>71.84504699707031</v>
+        <v>71.83349609375</v>
       </c>
       <c r="D10" t="n">
         <v>71.78</v>
@@ -742,16 +742,16 @@
         <v>71.40000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.06504699707031136</v>
+        <v>-0.05349609374999886</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06504699707031136</v>
+        <v>0.05349609374999886</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.09061994576527077</v>
+        <v>-0.0745278542072985</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -764,7 +764,7 @@
         <v>2019</v>
       </c>
       <c r="C11" t="n">
-        <v>73.59629058837891</v>
+        <v>73.65045928955078</v>
       </c>
       <c r="D11" t="n">
         <v>73.61</v>
@@ -773,16 +773,16 @@
         <v>73.15000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01370941162109318</v>
+        <v>-0.04045928955078182</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01370941162109318</v>
+        <v>0.04045928955078182</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01862438747601302</v>
+        <v>-0.05496439281453853</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -795,7 +795,7 @@
         <v>2019</v>
       </c>
       <c r="C12" t="n">
-        <v>69.09439086914062</v>
+        <v>69.13896179199219</v>
       </c>
       <c r="D12" t="n">
         <v>67.91</v>
@@ -804,13 +804,13 @@
         <v>68.44</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.184390869140628</v>
+        <v>-1.228961791992191</v>
       </c>
       <c r="G12" t="n">
-        <v>1.184390869140628</v>
+        <v>1.228961791992191</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.744059592314281</v>
+        <v>-1.80969193342982</v>
       </c>
       <c r="I12" t="n">
         <v>84</v>
@@ -826,7 +826,7 @@
         <v>2019</v>
       </c>
       <c r="C13" t="n">
-        <v>72.34585571289062</v>
+        <v>72.44762420654297</v>
       </c>
       <c r="D13" t="n">
         <v>72.81999999999999</v>
@@ -835,16 +835,16 @@
         <v>72.55</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4741442871093682</v>
+        <v>0.3723757934570244</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4741442871093682</v>
+        <v>0.3723757934570244</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6511182190460975</v>
+        <v>0.5113647259777869</v>
       </c>
       <c r="I13" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -857,7 +857,7 @@
         <v>2019</v>
       </c>
       <c r="C14" t="n">
-        <v>71.20256042480469</v>
+        <v>71.207275390625</v>
       </c>
       <c r="D14" t="n">
         <v>71.41</v>
@@ -866,16 +866,16 @@
         <v>70.92</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2074395751953091</v>
+        <v>0.2027246093749966</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2074395751953091</v>
+        <v>0.2027246093749966</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2904909329159909</v>
+        <v>0.2838882640736544</v>
       </c>
       <c r="I14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -888,7 +888,7 @@
         <v>2019</v>
       </c>
       <c r="C15" t="n">
-        <v>69.71009826660156</v>
+        <v>69.73345947265625</v>
       </c>
       <c r="D15" t="n">
         <v>69.73</v>
@@ -897,16 +897,16 @@
         <v>69.45999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01990173339844148</v>
+        <v>-0.003459472656246021</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01990173339844148</v>
+        <v>0.003459472656246021</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02854113494685426</v>
+        <v>-0.004961240006089231</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -919,7 +919,7 @@
         <v>2019</v>
       </c>
       <c r="C16" t="n">
-        <v>76.20866394042969</v>
+        <v>76.24031829833984</v>
       </c>
       <c r="D16" t="n">
         <v>76.2</v>
@@ -928,16 +928,16 @@
         <v>76.08</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.008663940429684658</v>
+        <v>-0.04031829833984091</v>
       </c>
       <c r="G16" t="n">
-        <v>0.008663940429684658</v>
+        <v>0.04031829833984091</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.01137000056389063</v>
+        <v>-0.05291115267695656</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -950,7 +950,7 @@
         <v>2019</v>
       </c>
       <c r="C17" t="n">
-        <v>73.34981536865234</v>
+        <v>73.3775634765625</v>
       </c>
       <c r="D17" t="n">
         <v>73.53</v>
@@ -959,16 +959,16 @@
         <v>72.89</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1801846313476574</v>
+        <v>0.1524365234375011</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1801846313476574</v>
+        <v>0.1524365234375011</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2450491382397081</v>
+        <v>0.2073120133788945</v>
       </c>
       <c r="I17" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
@@ -981,7 +981,7 @@
         <v>2019</v>
       </c>
       <c r="C18" t="n">
-        <v>72.70850372314453</v>
+        <v>72.79765319824219</v>
       </c>
       <c r="D18" t="n">
         <v>72.79000000000001</v>
@@ -990,16 +990,16 @@
         <v>72.27</v>
       </c>
       <c r="F18" t="n">
-        <v>0.081496276855475</v>
+        <v>-0.007653198242181247</v>
       </c>
       <c r="G18" t="n">
-        <v>0.081496276855475</v>
+        <v>0.007653198242181247</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1119608144737945</v>
+        <v>-0.0105140791896981</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1012,7 +1012,7 @@
         <v>2019</v>
       </c>
       <c r="C19" t="n">
-        <v>69.99062347412109</v>
+        <v>69.99468994140625</v>
       </c>
       <c r="D19" t="n">
         <v>69.91</v>
@@ -1021,16 +1021,16 @@
         <v>69.52</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.08062347412109716</v>
+        <v>-0.08468994140625341</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08062347412109716</v>
+        <v>0.08468994140625341</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1153246661723604</v>
+        <v>-0.1211413837880896</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -1043,7 +1043,7 @@
         <v>2019</v>
       </c>
       <c r="C20" t="n">
-        <v>75.64826202392578</v>
+        <v>75.64467620849609</v>
       </c>
       <c r="D20" t="n">
         <v>75.7</v>
@@ -1052,16 +1052,16 @@
         <v>75.68000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05173797607422159</v>
+        <v>0.05532379150390909</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05173797607422159</v>
+        <v>0.05532379150390909</v>
       </c>
       <c r="H20" t="n">
-        <v>0.06834607143226101</v>
+        <v>0.07308294782550739</v>
       </c>
       <c r="I20" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1074,7 +1074,7 @@
         <v>2019</v>
       </c>
       <c r="C21" t="n">
-        <v>69.65187072753906</v>
+        <v>69.58278656005859</v>
       </c>
       <c r="D21" t="n">
         <v>69.69</v>
@@ -1083,16 +1083,16 @@
         <v>69.23999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.03812927246093523</v>
+        <v>0.107213439941404</v>
       </c>
       <c r="G21" t="n">
-        <v>0.03812927246093523</v>
+        <v>0.107213439941404</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05471268827799573</v>
+        <v>0.1538433633827005</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
@@ -1105,7 +1105,7 @@
         <v>2019</v>
       </c>
       <c r="C22" t="n">
-        <v>72.62787628173828</v>
+        <v>72.56046295166016</v>
       </c>
       <c r="D22" t="n">
         <v>72.48</v>
@@ -1114,16 +1114,16 @@
         <v>72.08</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1478762817382773</v>
+        <v>-0.08046295166015227</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1478762817382773</v>
+        <v>0.08046295166015227</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2040235675196982</v>
+        <v>-0.1110140061536317</v>
       </c>
       <c r="I22" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -1136,7 +1136,7 @@
         <v>2019</v>
       </c>
       <c r="C23" t="n">
-        <v>71.82438659667969</v>
+        <v>71.83441162109375</v>
       </c>
       <c r="D23" t="n">
         <v>71.83</v>
@@ -1145,16 +1145,16 @@
         <v>71.42</v>
       </c>
       <c r="F23" t="n">
-        <v>0.005613403320310795</v>
+        <v>-0.004411621093751705</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005613403320310795</v>
+        <v>0.004411621093751705</v>
       </c>
       <c r="H23" t="n">
-        <v>0.007814845218308221</v>
+        <v>-0.006141752880066414</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1167,7 +1167,7 @@
         <v>2019</v>
       </c>
       <c r="C24" t="n">
-        <v>74.35444641113281</v>
+        <v>74.32083892822266</v>
       </c>
       <c r="D24" t="n">
         <v>74.05</v>
@@ -1176,16 +1176,16 @@
         <v>74.41</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3044464111328153</v>
+        <v>-0.2708389282226591</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3044464111328153</v>
+        <v>0.2708389282226591</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4111362743184542</v>
+        <v>-0.3657514223128415</v>
       </c>
       <c r="I24" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25">
@@ -1198,7 +1198,7 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>71.13002014160156</v>
+        <v>71.20153045654297</v>
       </c>
       <c r="D25" t="n">
         <v>71.23</v>
@@ -1207,16 +1207,16 @@
         <v>70.77</v>
       </c>
       <c r="F25" t="n">
-        <v>0.09997985839844148</v>
+        <v>0.02846954345703523</v>
       </c>
       <c r="G25" t="n">
-        <v>0.09997985839844148</v>
+        <v>0.02846954345703523</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1403620081404485</v>
+        <v>0.03996847319533234</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -1229,7 +1229,7 @@
         <v>2019</v>
       </c>
       <c r="C26" t="n">
-        <v>70.62802124023438</v>
+        <v>70.63937377929688</v>
       </c>
       <c r="D26" t="n">
         <v>70.75</v>
@@ -1238,16 +1238,16 @@
         <v>70.45999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.121978759765625</v>
+        <v>0.110626220703125</v>
       </c>
       <c r="G26" t="n">
-        <v>0.121978759765625</v>
+        <v>0.110626220703125</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1724081410114841</v>
+        <v>0.1563621494037103</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
@@ -1260,7 +1260,7 @@
         <v>2019</v>
       </c>
       <c r="C27" t="n">
-        <v>72.22074890136719</v>
+        <v>72.15231323242188</v>
       </c>
       <c r="D27" t="n">
         <v>72.18000000000001</v>
@@ -1269,16 +1269,16 @@
         <v>71.84</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.04074890136718068</v>
+        <v>0.02768676757813182</v>
       </c>
       <c r="G27" t="n">
-        <v>0.04074890136718068</v>
+        <v>0.02768676757813182</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.05645455994344787</v>
+        <v>0.03835794898605129</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1291,7 +1291,7 @@
         <v>2019</v>
       </c>
       <c r="C28" t="n">
-        <v>73.82752227783203</v>
+        <v>73.8497314453125</v>
       </c>
       <c r="D28" t="n">
         <v>73.90000000000001</v>
@@ -1300,16 +1300,16 @@
         <v>73.3</v>
       </c>
       <c r="F28" t="n">
-        <v>0.07247772216797443</v>
+        <v>0.05026855468750568</v>
       </c>
       <c r="G28" t="n">
-        <v>0.07247772216797443</v>
+        <v>0.05026855468750568</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09807540212175159</v>
+        <v>0.0680224014715909</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -1322,7 +1322,7 @@
         <v>2019</v>
       </c>
       <c r="C29" t="n">
-        <v>73.14033508300781</v>
+        <v>73.1419677734375</v>
       </c>
       <c r="D29" t="n">
         <v>73.38</v>
@@ -1331,16 +1331,16 @@
         <v>72.66</v>
       </c>
       <c r="F29" t="n">
-        <v>0.239664916992183</v>
+        <v>0.2380322265624955</v>
       </c>
       <c r="G29" t="n">
-        <v>0.239664916992183</v>
+        <v>0.2380322265624955</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3266079544728577</v>
+        <v>0.32438297432883</v>
       </c>
       <c r="I29" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30">
@@ -1353,7 +1353,7 @@
         <v>2019</v>
       </c>
       <c r="C30" t="n">
-        <v>69.82093811035156</v>
+        <v>69.81037902832031</v>
       </c>
       <c r="D30" t="n">
         <v>69.23</v>
@@ -1362,16 +1362,16 @@
         <v>69.23999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.5909381103515585</v>
+        <v>-0.5803790283203085</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5909381103515585</v>
+        <v>0.5803790283203085</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.8535867548050823</v>
+        <v>-0.8383345779579785</v>
       </c>
       <c r="I30" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31">
@@ -1384,7 +1384,7 @@
         <v>2019</v>
       </c>
       <c r="C31" t="n">
-        <v>74.41120910644531</v>
+        <v>74.42060089111328</v>
       </c>
       <c r="D31" t="n">
         <v>74.67</v>
@@ -1393,16 +1393,16 @@
         <v>74.28</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2587908935546892</v>
+        <v>0.2493991088867205</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2587908935546892</v>
+        <v>0.2493991088867205</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3465794744270647</v>
+        <v>0.3340017528950321</v>
       </c>
       <c r="I31" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32">
@@ -1415,7 +1415,7 @@
         <v>2019</v>
       </c>
       <c r="C32" t="n">
-        <v>71.49912261962891</v>
+        <v>71.50505065917969</v>
       </c>
       <c r="D32" t="n">
         <v>71.04000000000001</v>
@@ -1424,16 +1424,16 @@
         <v>71.09</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4591226196289</v>
+        <v>-0.4650506591796812</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4591226196289</v>
+        <v>0.4650506591796812</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6462874713244651</v>
+        <v>-0.6546321215930198</v>
       </c>
       <c r="I32" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33">
@@ -1446,7 +1446,7 @@
         <v>2019</v>
       </c>
       <c r="C33" t="n">
-        <v>71.56993103027344</v>
+        <v>71.63294982910156</v>
       </c>
       <c r="D33" t="n">
         <v>72.55</v>
@@ -1455,13 +1455,13 @@
         <v>71.41</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9800689697265597</v>
+        <v>0.9170501708984347</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9800689697265597</v>
+        <v>0.9170501708984347</v>
       </c>
       <c r="H33" t="n">
-        <v>1.350887621952529</v>
+        <v>1.264025046035058</v>
       </c>
       <c r="I33" t="n">
         <v>82</v>
@@ -1477,7 +1477,7 @@
         <v>2019</v>
       </c>
       <c r="C34" t="n">
-        <v>72.04017639160156</v>
+        <v>71.92510223388672</v>
       </c>
       <c r="D34" t="n">
         <v>72.19</v>
@@ -1486,16 +1486,16 @@
         <v>71.59</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1498236083984352</v>
+        <v>0.264897766113279</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1498236083984352</v>
+        <v>0.264897766113279</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2075406682344303</v>
+        <v>0.3669452363392146</v>
       </c>
       <c r="I34" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35">
@@ -1508,7 +1508,7 @@
         <v>2019</v>
       </c>
       <c r="C35" t="n">
-        <v>70.57400512695312</v>
+        <v>70.58500671386719</v>
       </c>
       <c r="D35" t="n">
         <v>70.33</v>
@@ -1517,13 +1517,13 @@
         <v>70.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2440051269531267</v>
+        <v>-0.2550067138671892</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2440051269531267</v>
+        <v>0.2550067138671892</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3469431635903977</v>
+        <v>-0.3625859716581675</v>
       </c>
       <c r="I35" t="n">
         <v>48</v>
@@ -1539,7 +1539,7 @@
         <v>2019</v>
       </c>
       <c r="C36" t="n">
-        <v>72.27067565917969</v>
+        <v>72.33314514160156</v>
       </c>
       <c r="D36" t="n">
         <v>72.37</v>
@@ -1548,16 +1548,16 @@
         <v>71.93000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.09932434082031705</v>
+        <v>0.03685485839844205</v>
       </c>
       <c r="G36" t="n">
-        <v>0.09932434082031705</v>
+        <v>0.03685485839844205</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1372451856022068</v>
+        <v>0.05092560231925113</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -1570,7 +1570,7 @@
         <v>2019</v>
       </c>
       <c r="C37" t="n">
-        <v>72.21551513671875</v>
+        <v>72.22038269042969</v>
       </c>
       <c r="D37" t="n">
         <v>72.29000000000001</v>
@@ -1579,16 +1579,16 @@
         <v>71.93000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>0.07448486328125625</v>
+        <v>0.06961730957031875</v>
       </c>
       <c r="G37" t="n">
-        <v>0.07448486328125625</v>
+        <v>0.06961730957031875</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1030361921168298</v>
+        <v>0.09630282137269158</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
@@ -1601,7 +1601,7 @@
         <v>2019</v>
       </c>
       <c r="C38" t="n">
-        <v>71.73126220703125</v>
+        <v>71.73436737060547</v>
       </c>
       <c r="D38" t="n">
         <v>71.81</v>
@@ -1610,16 +1610,16 @@
         <v>71.23999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>0.07873779296875227</v>
+        <v>0.07563262939453352</v>
       </c>
       <c r="G38" t="n">
-        <v>0.07873779296875227</v>
+        <v>0.07563262939453352</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1096473930772208</v>
+        <v>0.1053232549708029</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
@@ -1632,7 +1632,7 @@
         <v>2019</v>
       </c>
       <c r="C39" t="n">
-        <v>71.81109619140625</v>
+        <v>71.81256103515625</v>
       </c>
       <c r="D39" t="n">
         <v>72.45999999999999</v>
@@ -1641,13 +1641,13 @@
         <v>71.48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6489038085937437</v>
+        <v>0.6474389648437437</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6489038085937437</v>
+        <v>0.6474389648437437</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8955338236181946</v>
+        <v>0.8935122341205408</v>
       </c>
       <c r="I39" t="n">
         <v>76</v>
@@ -1663,7 +1663,7 @@
         <v>2019</v>
       </c>
       <c r="C40" t="n">
-        <v>73.42095184326172</v>
+        <v>73.43663787841797</v>
       </c>
       <c r="D40" t="n">
         <v>73.34999999999999</v>
@@ -1672,16 +1672,16 @@
         <v>73</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.07095184326172443</v>
+        <v>-0.08663787841797443</v>
       </c>
       <c r="G40" t="n">
-        <v>0.07095184326172443</v>
+        <v>0.08663787841797443</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.09673052932750435</v>
+        <v>-0.1181157169979202</v>
       </c>
       <c r="I40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
@@ -1694,7 +1694,7 @@
         <v>2019</v>
       </c>
       <c r="C41" t="n">
-        <v>71.00736999511719</v>
+        <v>70.99003601074219</v>
       </c>
       <c r="D41" t="n">
         <v>71.25</v>
@@ -1703,16 +1703,16 @@
         <v>70.67</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2426300048828125</v>
+        <v>0.2599639892578125</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2426300048828125</v>
+        <v>0.2599639892578125</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3405333401864035</v>
+        <v>0.3648617393092105</v>
       </c>
       <c r="I41" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42">
@@ -1725,7 +1725,7 @@
         <v>2019</v>
       </c>
       <c r="C42" t="n">
-        <v>70.59313201904297</v>
+        <v>70.60038757324219</v>
       </c>
       <c r="D42" t="n">
         <v>70.42</v>
@@ -1734,16 +1734,16 @@
         <v>70.38</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.173132019042967</v>
+        <v>-0.1803875732421858</v>
       </c>
       <c r="G42" t="n">
-        <v>0.173132019042967</v>
+        <v>0.1803875732421858</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.2458563178684565</v>
+        <v>-0.2561595757486308</v>
       </c>
       <c r="I42" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43">
@@ -1756,7 +1756,7 @@
         <v>2019</v>
       </c>
       <c r="C43" t="n">
-        <v>70.55945587158203</v>
+        <v>70.61293792724609</v>
       </c>
       <c r="D43" t="n">
         <v>70.38</v>
@@ -1765,16 +1765,16 @@
         <v>69.95</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.1794558715820358</v>
+        <v>-0.2329379272460983</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1794558715820358</v>
+        <v>0.2329379272460983</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.2549813463797042</v>
+        <v>-0.330971763634695</v>
       </c>
       <c r="I43" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -1787,7 +1787,7 @@
         <v>2019</v>
       </c>
       <c r="C44" t="n">
-        <v>73.925048828125</v>
+        <v>74.03375244140625</v>
       </c>
       <c r="D44" t="n">
         <v>74.13</v>
@@ -1796,16 +1796,16 @@
         <v>73.81</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2049511718749955</v>
+        <v>0.09624755859374545</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2049511718749955</v>
+        <v>0.09624755859374545</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2764753431471678</v>
+        <v>0.1298361777873269</v>
       </c>
       <c r="I44" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45">
@@ -1818,7 +1818,7 @@
         <v>2019</v>
       </c>
       <c r="C45" t="n">
-        <v>70.58021545410156</v>
+        <v>70.59593963623047</v>
       </c>
       <c r="D45" t="n">
         <v>69.78</v>
@@ -1827,13 +1827,13 @@
         <v>70.17</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.8002154541015614</v>
+        <v>-0.8159396362304676</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8002154541015614</v>
+        <v>0.8159396362304676</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.146769065780398</v>
+        <v>-1.169303004056273</v>
       </c>
       <c r="I45" t="n">
         <v>79</v>
@@ -1849,7 +1849,7 @@
         <v>2019</v>
       </c>
       <c r="C46" t="n">
-        <v>72.63479614257812</v>
+        <v>72.70447540283203</v>
       </c>
       <c r="D46" t="n">
         <v>72.81999999999999</v>
@@ -1858,16 +1858,16 @@
         <v>72.23</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1852038574218682</v>
+        <v>0.1155245971679619</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1852038574218682</v>
+        <v>0.1155245971679619</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2543310318894098</v>
+        <v>0.1586440499422713</v>
       </c>
       <c r="I46" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47">
@@ -1880,7 +1880,7 @@
         <v>2019</v>
       </c>
       <c r="C47" t="n">
-        <v>71.06867980957031</v>
+        <v>71.05336761474609</v>
       </c>
       <c r="D47" t="n">
         <v>70.70999999999999</v>
@@ -1889,16 +1889,16 @@
         <v>70.76000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.3586798095703188</v>
+        <v>-0.3433676147461</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3586798095703188</v>
+        <v>0.3433676147461</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.5072547158397946</v>
+        <v>-0.4855997945779946</v>
       </c>
       <c r="I47" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48">
@@ -1911,7 +1911,7 @@
         <v>2019</v>
       </c>
       <c r="C48" t="n">
-        <v>77.86098480224609</v>
+        <v>77.85194396972656</v>
       </c>
       <c r="D48" t="n">
         <v>79.03</v>
@@ -1920,13 +1920,13 @@
         <v>78.59999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>1.169015197753907</v>
+        <v>1.178056030273439</v>
       </c>
       <c r="G48" t="n">
-        <v>1.169015197753907</v>
+        <v>1.178056030273439</v>
       </c>
       <c r="H48" t="n">
-        <v>1.47920434993535</v>
+        <v>1.49064409752428</v>
       </c>
       <c r="I48" t="n">
         <v>83</v>
@@ -1942,7 +1942,7 @@
         <v>2019</v>
       </c>
       <c r="C49" t="n">
-        <v>78.79345703125</v>
+        <v>78.76188659667969</v>
       </c>
       <c r="D49" t="n">
         <v>79.64</v>
@@ -1951,13 +1951,13 @@
         <v>79.31</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8465429687500006</v>
+        <v>0.8781134033203131</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8465429687500006</v>
+        <v>0.8781134033203131</v>
       </c>
       <c r="H49" t="n">
-        <v>1.062962040118032</v>
+        <v>1.102603469764331</v>
       </c>
       <c r="I49" t="n">
         <v>81</v>
@@ -1973,7 +1973,7 @@
         <v>2019</v>
       </c>
       <c r="C50" t="n">
-        <v>73.80203247070312</v>
+        <v>73.74412536621094</v>
       </c>
       <c r="D50" t="n">
         <v>74.54000000000001</v>
@@ -1982,16 +1982,16 @@
         <v>73.63</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7379675292968813</v>
+        <v>0.7958746337890688</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7379675292968813</v>
+        <v>0.7958746337890688</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9900288828774901</v>
+        <v>1.067714829338702</v>
       </c>
       <c r="I50" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51">
@@ -2004,7 +2004,7 @@
         <v>2019</v>
       </c>
       <c r="C51" t="n">
-        <v>69.97848510742188</v>
+        <v>69.96859741210938</v>
       </c>
       <c r="D51" t="n">
         <v>70.44</v>
@@ -2013,16 +2013,16 @@
         <v>69.66</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4615148925781227</v>
+        <v>0.4714025878906227</v>
       </c>
       <c r="G51" t="n">
-        <v>0.4615148925781227</v>
+        <v>0.4714025878906227</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6551886606730873</v>
+        <v>0.6692257068293906</v>
       </c>
       <c r="I51" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52">
@@ -2035,7 +2035,7 @@
         <v>2019</v>
       </c>
       <c r="C52" t="n">
-        <v>70.86129760742188</v>
+        <v>70.95203399658203</v>
       </c>
       <c r="D52" t="n">
         <v>70.78</v>
@@ -2044,16 +2044,16 @@
         <v>70.61</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.08129760742187386</v>
+        <v>-0.1720339965820301</v>
       </c>
       <c r="G52" t="n">
-        <v>0.08129760742187386</v>
+        <v>0.1720339965820301</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1148595753346621</v>
+        <v>-0.243054530350424</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53">
@@ -2066,7 +2066,7 @@
         <v>2019</v>
       </c>
       <c r="C53" t="n">
-        <v>72.58427429199219</v>
+        <v>72.60232543945312</v>
       </c>
       <c r="D53" t="n">
         <v>72.73999999999999</v>
@@ -2075,13 +2075,13 @@
         <v>72.25</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1557257080078074</v>
+        <v>0.1376745605468699</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1557257080078074</v>
+        <v>0.1376745605468699</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2140853835686106</v>
+        <v>0.1892693986071898</v>
       </c>
       <c r="I53" t="n">
         <v>33</v>
@@ -2097,7 +2097,7 @@
         <v>2019</v>
       </c>
       <c r="C54" t="n">
-        <v>72.46143341064453</v>
+        <v>72.46271514892578</v>
       </c>
       <c r="D54" t="n">
         <v>72.95</v>
@@ -2106,16 +2106,16 @@
         <v>72.03</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4885665893554716</v>
+        <v>0.4872848510742216</v>
       </c>
       <c r="G54" t="n">
-        <v>0.4885665893554716</v>
+        <v>0.4872848510742216</v>
       </c>
       <c r="H54" t="n">
-        <v>0.669728018307706</v>
+        <v>0.6679710090119555</v>
       </c>
       <c r="I54" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55">
@@ -2128,7 +2128,7 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>73.84915161132812</v>
+        <v>73.87834167480469</v>
       </c>
       <c r="D55" t="n">
         <v>74.14</v>
@@ -2137,16 +2137,16 @@
         <v>73.83</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2908483886718756</v>
+        <v>0.2616583251953131</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2908483886718756</v>
+        <v>0.2616583251953131</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3922961811058478</v>
+        <v>0.3529246360875547</v>
       </c>
       <c r="I55" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56">
@@ -2159,7 +2159,7 @@
         <v>2019</v>
       </c>
       <c r="C56" t="n">
-        <v>69.33306884765625</v>
+        <v>69.33049011230469</v>
       </c>
       <c r="D56" t="n">
         <v>68.48999999999999</v>
@@ -2168,13 +2168,13 @@
         <v>68.66</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.8430688476562551</v>
+        <v>-0.8404901123046926</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8430688476562551</v>
+        <v>0.8404901123046926</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.230937140686604</v>
+        <v>-1.22717201387749</v>
       </c>
       <c r="I56" t="n">
         <v>80</v>
@@ -2190,7 +2190,7 @@
         <v>2019</v>
       </c>
       <c r="C57" t="n">
-        <v>75.60360717773438</v>
+        <v>75.5572509765625</v>
       </c>
       <c r="D57" t="n">
         <v>75.39</v>
@@ -2199,16 +2199,16 @@
         <v>75.39</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2136071777343744</v>
+        <v>-0.1672509765624994</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2136071777343744</v>
+        <v>0.1672509765624994</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.283336221958316</v>
+        <v>-0.221847694074147</v>
       </c>
       <c r="I57" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58">
@@ -2221,7 +2221,7 @@
         <v>2019</v>
       </c>
       <c r="C58" t="n">
-        <v>74.82454681396484</v>
+        <v>74.84114837646484</v>
       </c>
       <c r="D58" t="n">
         <v>75.23999999999999</v>
@@ -2230,13 +2230,13 @@
         <v>74.55</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4154531860351511</v>
+        <v>0.3988516235351511</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4154531860351511</v>
+        <v>0.3988516235351511</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5521706353470909</v>
+        <v>0.5301058260701106</v>
       </c>
       <c r="I58" t="n">
         <v>62</v>
@@ -2252,7 +2252,7 @@
         <v>2019</v>
       </c>
       <c r="C59" t="n">
-        <v>66.89926147460938</v>
+        <v>66.87986755371094</v>
       </c>
       <c r="D59" t="n">
         <v>67.5</v>
@@ -2261,13 +2261,13 @@
         <v>66.42</v>
       </c>
       <c r="F59" t="n">
-        <v>0.600738525390625</v>
+        <v>0.6201324462890625</v>
       </c>
       <c r="G59" t="n">
-        <v>0.600738525390625</v>
+        <v>0.6201324462890625</v>
       </c>
       <c r="H59" t="n">
-        <v>0.8899830005787037</v>
+        <v>0.9187147352430555</v>
       </c>
       <c r="I59" t="n">
         <v>75</v>
@@ -2283,7 +2283,7 @@
         <v>2019</v>
       </c>
       <c r="C60" t="n">
-        <v>71.43608093261719</v>
+        <v>71.44516754150391</v>
       </c>
       <c r="D60" t="n">
         <v>71.09999999999999</v>
@@ -2292,16 +2292,16 @@
         <v>71.2</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3360809326171932</v>
+        <v>-0.3451675415039119</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3360809326171932</v>
+        <v>0.3451675415039119</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.4726876689412</v>
+        <v>-0.4854677095694964</v>
       </c>
       <c r="I60" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61">
@@ -2314,7 +2314,7 @@
         <v>2019</v>
       </c>
       <c r="C61" t="n">
-        <v>73.70333099365234</v>
+        <v>73.69167327880859</v>
       </c>
       <c r="D61" t="n">
         <v>73.66</v>
@@ -2323,16 +2323,16 @@
         <v>73.18000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.04333099365234716</v>
+        <v>-0.03167327880859716</v>
       </c>
       <c r="G61" t="n">
-        <v>0.04333099365234716</v>
+        <v>0.03167327880859716</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.05882567696490247</v>
+        <v>-0.04299929243632523</v>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -2345,7 +2345,7 @@
         <v>2019</v>
       </c>
       <c r="C62" t="n">
-        <v>73.29065704345703</v>
+        <v>73.29074096679688</v>
       </c>
       <c r="D62" t="n">
         <v>73.22</v>
@@ -2354,16 +2354,16 @@
         <v>72.86</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.07065704345703239</v>
+        <v>-0.07074096679687614</v>
       </c>
       <c r="G62" t="n">
-        <v>0.07065704345703239</v>
+        <v>0.07074096679687614</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.09649964962719529</v>
+        <v>-0.09661426768215807</v>
       </c>
       <c r="I62" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63">
@@ -2376,7 +2376,7 @@
         <v>2019</v>
       </c>
       <c r="C63" t="n">
-        <v>72.65031433105469</v>
+        <v>72.64373016357422</v>
       </c>
       <c r="D63" t="n">
         <v>72.84</v>
@@ -2385,13 +2385,13 @@
         <v>72.38</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1896856689453159</v>
+        <v>0.1962698364257847</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1896856689453159</v>
+        <v>0.1962698364257847</v>
       </c>
       <c r="H63" t="n">
-        <v>0.260414152862872</v>
+        <v>0.2694533723582985</v>
       </c>
       <c r="I63" t="n">
         <v>39</v>
@@ -2407,7 +2407,7 @@
         <v>2019</v>
       </c>
       <c r="C64" t="n">
-        <v>73.61566925048828</v>
+        <v>73.61924743652344</v>
       </c>
       <c r="D64" t="n">
         <v>73.28</v>
@@ -2416,16 +2416,16 @@
         <v>73.13</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.3356692504882801</v>
+        <v>-0.3392474365234364</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3356692504882801</v>
+        <v>0.3392474365234364</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.4580639335265831</v>
+        <v>-0.4629468293169164</v>
       </c>
       <c r="I64" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65">
@@ -2438,7 +2438,7 @@
         <v>2019</v>
       </c>
       <c r="C65" t="n">
-        <v>70.45670318603516</v>
+        <v>70.45220184326172</v>
       </c>
       <c r="D65" t="n">
         <v>70.39</v>
@@ -2447,16 +2447,16 @@
         <v>69.98999999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.06670318603515568</v>
+        <v>-0.06220184326171818</v>
       </c>
       <c r="G65" t="n">
-        <v>0.06670318603515568</v>
+        <v>0.06220184326171818</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.09476230435453285</v>
+        <v>-0.08836744319039379</v>
       </c>
       <c r="I65" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66">
@@ -2469,7 +2469,7 @@
         <v>2019</v>
       </c>
       <c r="C66" t="n">
-        <v>71.55217742919922</v>
+        <v>71.56295776367188</v>
       </c>
       <c r="D66" t="n">
         <v>71.79000000000001</v>
@@ -2478,16 +2478,16 @@
         <v>71.27</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2378225708007875</v>
+        <v>0.2270422363281313</v>
       </c>
       <c r="G66" t="n">
-        <v>0.2378225708007875</v>
+        <v>0.2270422363281313</v>
       </c>
       <c r="H66" t="n">
-        <v>0.3312753458709952</v>
+        <v>0.3162588610226093</v>
       </c>
       <c r="I66" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67">
@@ -2500,7 +2500,7 @@
         <v>2019</v>
       </c>
       <c r="C67" t="n">
-        <v>71.16107940673828</v>
+        <v>71.15520477294922</v>
       </c>
       <c r="D67" t="n">
         <v>71.66</v>
@@ -2509,16 +2509,16 @@
         <v>70.95999999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>0.4989205932617153</v>
+        <v>0.5047952270507778</v>
       </c>
       <c r="G67" t="n">
-        <v>0.4989205932617153</v>
+        <v>0.5047952270507778</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6962330355312801</v>
+        <v>0.7044309615556488</v>
       </c>
       <c r="I67" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68">
@@ -2531,7 +2531,7 @@
         <v>2019</v>
       </c>
       <c r="C68" t="n">
-        <v>74.46784973144531</v>
+        <v>74.25026702880859</v>
       </c>
       <c r="D68" t="n">
         <v>74.77</v>
@@ -2540,16 +2540,16 @@
         <v>74.28</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3021502685546835</v>
+        <v>0.5197329711914023</v>
       </c>
       <c r="G68" t="n">
-        <v>0.3021502685546835</v>
+        <v>0.5197329711914023</v>
       </c>
       <c r="H68" t="n">
-        <v>0.4041062840105437</v>
+        <v>0.6951089624065833</v>
       </c>
       <c r="I68" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69">
@@ -2562,7 +2562,7 @@
         <v>2019</v>
       </c>
       <c r="C69" t="n">
-        <v>73.30699157714844</v>
+        <v>73.30352020263672</v>
       </c>
       <c r="D69" t="n">
         <v>73.43000000000001</v>
@@ -2571,16 +2571,16 @@
         <v>72.86</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1230084228515693</v>
+        <v>0.1264797973632881</v>
       </c>
       <c r="G69" t="n">
-        <v>0.1230084228515693</v>
+        <v>0.1264797973632881</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1675179393321113</v>
+        <v>0.1722454001951356</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70">
@@ -2593,7 +2593,7 @@
         <v>2019</v>
       </c>
       <c r="C70" t="n">
-        <v>70.70478820800781</v>
+        <v>70.70780181884766</v>
       </c>
       <c r="D70" t="n">
         <v>71.2</v>
@@ -2602,16 +2602,16 @@
         <v>70.44</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4952117919921903</v>
+        <v>0.4921981811523466</v>
       </c>
       <c r="G70" t="n">
-        <v>0.4952117919921903</v>
+        <v>0.4921981811523466</v>
       </c>
       <c r="H70" t="n">
-        <v>0.6955221797643123</v>
+        <v>0.6912895802701496</v>
       </c>
       <c r="I70" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71">
@@ -2624,7 +2624,7 @@
         <v>2019</v>
       </c>
       <c r="C71" t="n">
-        <v>73.36508178710938</v>
+        <v>73.36776733398438</v>
       </c>
       <c r="D71" t="n">
         <v>72.93000000000001</v>
@@ -2633,16 +2633,16 @@
         <v>72.91</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.4350817871093682</v>
+        <v>-0.4377673339843682</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4350817871093682</v>
+        <v>0.4377673339843682</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.5965745058403512</v>
+        <v>-0.6002568682083754</v>
       </c>
       <c r="I71" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="72">
@@ -2655,7 +2655,7 @@
         <v>2019</v>
       </c>
       <c r="C72" t="n">
-        <v>72.61825561523438</v>
+        <v>72.54518127441406</v>
       </c>
       <c r="D72" t="n">
         <v>72.58</v>
@@ -2664,16 +2664,16 @@
         <v>72.09</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.03825561523437671</v>
+        <v>0.03481872558593579</v>
       </c>
       <c r="G72" t="n">
-        <v>0.03825561523437671</v>
+        <v>0.03481872558593579</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.05270820506251958</v>
+        <v>0.04797289278855855</v>
       </c>
       <c r="I72" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -2686,7 +2686,7 @@
         <v>2019</v>
       </c>
       <c r="C73" t="n">
-        <v>73.93893432617188</v>
+        <v>73.85550689697266</v>
       </c>
       <c r="D73" t="n">
         <v>74.37</v>
@@ -2695,16 +2695,16 @@
         <v>73.68000000000001</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4310656738281295</v>
+        <v>0.5144931030273483</v>
       </c>
       <c r="G73" t="n">
-        <v>0.4310656738281295</v>
+        <v>0.5144931030273483</v>
       </c>
       <c r="H73" t="n">
-        <v>0.5796230655212176</v>
+        <v>0.6918019403352806</v>
       </c>
       <c r="I73" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74">
@@ -2717,7 +2717,7 @@
         <v>2019</v>
       </c>
       <c r="C74" t="n">
-        <v>72.70368194580078</v>
+        <v>72.63214874267578</v>
       </c>
       <c r="D74" t="n">
         <v>72.55</v>
@@ -2726,16 +2726,16 @@
         <v>72.23</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.1536819458007841</v>
+        <v>-0.08214874267578409</v>
       </c>
       <c r="G74" t="n">
-        <v>0.1536819458007841</v>
+        <v>0.08214874267578409</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.2118290086847472</v>
+        <v>-0.1132305205731001</v>
       </c>
       <c r="I74" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75">
@@ -2748,7 +2748,7 @@
         <v>2019</v>
       </c>
       <c r="C75" t="n">
-        <v>72.35346984863281</v>
+        <v>72.41527557373047</v>
       </c>
       <c r="D75" t="n">
         <v>72.76000000000001</v>
@@ -2757,16 +2757,16 @@
         <v>72</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4065301513671926</v>
+        <v>0.3447244262695364</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4065301513671926</v>
+        <v>0.3447244262695364</v>
       </c>
       <c r="H75" t="n">
-        <v>0.5587275307410563</v>
+        <v>0.4737828838228921</v>
       </c>
       <c r="I75" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76">
@@ -2779,7 +2779,7 @@
         <v>2019</v>
       </c>
       <c r="C76" t="n">
-        <v>70.55274963378906</v>
+        <v>70.5550537109375</v>
       </c>
       <c r="D76" t="n">
         <v>70.20999999999999</v>
@@ -2788,13 +2788,13 @@
         <v>70.31999999999999</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.3427496337890688</v>
+        <v>-0.3450537109375063</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3427496337890688</v>
+        <v>0.3450537109375063</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.4881778005826361</v>
+        <v>-0.4914594942850111</v>
       </c>
       <c r="I76" t="n">
         <v>59</v>
@@ -2810,7 +2810,7 @@
         <v>2019</v>
       </c>
       <c r="C77" t="n">
-        <v>74.57102966308594</v>
+        <v>74.51406860351562</v>
       </c>
       <c r="D77" t="n">
         <v>75.11</v>
@@ -2819,16 +2819,16 @@
         <v>74.34</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5389703369140619</v>
+        <v>0.5959313964843744</v>
       </c>
       <c r="G77" t="n">
-        <v>0.5389703369140619</v>
+        <v>0.5959313964843744</v>
       </c>
       <c r="H77" t="n">
-        <v>0.7175746730316361</v>
+        <v>0.7934115250757215</v>
       </c>
       <c r="I77" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78">
@@ -2841,7 +2841,7 @@
         <v>2019</v>
       </c>
       <c r="C78" t="n">
-        <v>71.99033355712891</v>
+        <v>71.924072265625</v>
       </c>
       <c r="D78" t="n">
         <v>72.08</v>
@@ -2850,16 +2850,16 @@
         <v>71.64</v>
       </c>
       <c r="F78" t="n">
-        <v>0.08966644287109204</v>
+        <v>0.1559277343749983</v>
       </c>
       <c r="G78" t="n">
-        <v>0.08966644287109204</v>
+        <v>0.1559277343749983</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1243985056480189</v>
+        <v>0.216325935592395</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79">
@@ -2872,7 +2872,7 @@
         <v>2019</v>
       </c>
       <c r="C79" t="n">
-        <v>75.47120666503906</v>
+        <v>75.49302673339844</v>
       </c>
       <c r="D79" t="n">
         <v>75.53</v>
@@ -2881,16 +2881,16 @@
         <v>75.17</v>
       </c>
       <c r="F79" t="n">
-        <v>0.05879333496093864</v>
+        <v>0.03697326660156364</v>
       </c>
       <c r="G79" t="n">
-        <v>0.05879333496093864</v>
+        <v>0.03697326660156364</v>
       </c>
       <c r="H79" t="n">
-        <v>0.07784103662245284</v>
+        <v>0.04895176301014648</v>
       </c>
       <c r="I79" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
@@ -2903,7 +2903,7 @@
         <v>2019</v>
       </c>
       <c r="C80" t="n">
-        <v>73.39144897460938</v>
+        <v>73.39276885986328</v>
       </c>
       <c r="D80" t="n">
         <v>73.34</v>
@@ -2912,16 +2912,16 @@
         <v>72.86</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.05144897460937159</v>
+        <v>-0.05276885986327784</v>
       </c>
       <c r="G80" t="n">
-        <v>0.05144897460937159</v>
+        <v>0.05276885986327784</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.07015131525684699</v>
+        <v>-0.07195099517763545</v>
       </c>
       <c r="I80" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81">
@@ -2934,7 +2934,7 @@
         <v>2019</v>
       </c>
       <c r="C81" t="n">
-        <v>64.27635192871094</v>
+        <v>64.27309417724609</v>
       </c>
       <c r="D81" t="n">
         <v>67.26000000000001</v>
@@ -2943,13 +2943,13 @@
         <v>63.02</v>
       </c>
       <c r="F81" t="n">
-        <v>2.983648071289068</v>
+        <v>2.986905822753911</v>
       </c>
       <c r="G81" t="n">
-        <v>2.983648071289068</v>
+        <v>2.986905822753911</v>
       </c>
       <c r="H81" t="n">
-        <v>4.435991780090793</v>
+        <v>4.440835299961212</v>
       </c>
       <c r="I81" t="n">
         <v>85</v>
@@ -2965,7 +2965,7 @@
         <v>2019</v>
       </c>
       <c r="C82" t="n">
-        <v>74.12704467773438</v>
+        <v>74.23114013671875</v>
       </c>
       <c r="D82" t="n">
         <v>74.20999999999999</v>
@@ -2974,16 +2974,16 @@
         <v>73.98</v>
       </c>
       <c r="F82" t="n">
-        <v>0.08295532226561875</v>
+        <v>-0.02114013671875625</v>
       </c>
       <c r="G82" t="n">
-        <v>0.08295532226561875</v>
+        <v>0.02114013671875625</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1117845603902692</v>
+        <v>-0.02848691108847359</v>
       </c>
       <c r="I82" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -2996,7 +2996,7 @@
         <v>2019</v>
       </c>
       <c r="C83" t="n">
-        <v>72.61693572998047</v>
+        <v>72.614013671875</v>
       </c>
       <c r="D83" t="n">
         <v>72.73999999999999</v>
@@ -3005,16 +3005,16 @@
         <v>72.09</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1230642700195261</v>
+        <v>0.1259863281249949</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1230642700195261</v>
+        <v>0.1259863281249949</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1691837641181278</v>
+        <v>0.1732008910159402</v>
       </c>
       <c r="I83" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84">
@@ -3027,7 +3027,7 @@
         <v>2019</v>
       </c>
       <c r="C84" t="n">
-        <v>77.65976715087891</v>
+        <v>77.6683349609375</v>
       </c>
       <c r="D84" t="n">
         <v>78.08</v>
@@ -3036,13 +3036,13 @@
         <v>77.55</v>
       </c>
       <c r="F84" t="n">
-        <v>0.420232849121092</v>
+        <v>0.4116650390624983</v>
       </c>
       <c r="G84" t="n">
-        <v>0.420232849121092</v>
+        <v>0.4116650390624983</v>
       </c>
       <c r="H84" t="n">
-        <v>0.5382080547145134</v>
+        <v>0.5272349373238964</v>
       </c>
       <c r="I84" t="n">
         <v>63</v>
@@ -3058,7 +3058,7 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>75.82109832763672</v>
+        <v>75.83530426025391</v>
       </c>
       <c r="D85" t="n">
         <v>76.38</v>
@@ -3067,16 +3067,16 @@
         <v>75.97</v>
       </c>
       <c r="F85" t="n">
-        <v>0.5589016723632767</v>
+        <v>0.5446957397460892</v>
       </c>
       <c r="G85" t="n">
-        <v>0.5589016723632767</v>
+        <v>0.5446957397460892</v>
       </c>
       <c r="H85" t="n">
-        <v>0.7317382460896528</v>
+        <v>0.7131392245955607</v>
       </c>
       <c r="I85" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86">
@@ -3089,7 +3089,7 @@
         <v>2019</v>
       </c>
       <c r="C86" t="n">
-        <v>74.96767425537109</v>
+        <v>74.97190093994141</v>
       </c>
       <c r="D86" t="n">
         <v>74.75</v>
@@ -3098,16 +3098,16 @@
         <v>74.58</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.2176742553710938</v>
+        <v>-0.2219009399414062</v>
       </c>
       <c r="G86" t="n">
-        <v>0.2176742553710938</v>
+        <v>0.2219009399414062</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.2912030172188545</v>
+        <v>-0.2968574447376672</v>
       </c>
       <c r="I86" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
